--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Ноябрь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Ноябрь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92555759833</v>
+        <v>46157.93113695576</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Ноябрь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Ноябрь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93113695576</v>
+        <v>46157.93137157689</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Ноябрь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Ноябрь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93137157689</v>
+        <v>46157.93384636223</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Ноябрь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Ноябрь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93384636223</v>
+        <v>46157.9369636211</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Ноябрь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Ноябрь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9369636211</v>
+        <v>46158.28205260437</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Ноябрь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Ноябрь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28205260437</v>
+        <v>46158.29653190979</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Ноябрь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Ноябрь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29653190979</v>
+        <v>46158.29808206082</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Ноябрь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Ноябрь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29808206082</v>
+        <v>46158.33370961543</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Ноябрь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Ноябрь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33370961543</v>
+        <v>46158.37222281167</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Ноябрь 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Ноябрь 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37222281167</v>
+        <v>46158.37275930055</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
